--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F524370A-2AA6-4156-AF6A-E23ABBC5770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC57978-F3B5-4A36-8573-78E38382A582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" firstSheet="1" activeTab="3" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Shorts'!$A$1:$E$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mapping-Tops'!$A$1:$E$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mapping-Track Pants'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mapping-Tshirts'!$A$3:$E$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mapping-Tshirts'!$A$2:$E$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -619,7 +619,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="252">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -1381,7 +1381,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1397,20 +1397,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1429,12 +1421,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1448,14 +1434,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -4859,7 +4842,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F62085-80E4-4F8B-99A1-7536229413A5}">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
@@ -4885,91 +4868,105 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>173</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" s="3" t="s">
+        <v>200</v>
       </c>
       <c r="C2" t="s">
         <v>146</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>200</v>
+      <c r="B4" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="C4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" t="s">
-        <v>146</v>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B6" s="4" t="s">
-        <v>202</v>
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="C6" t="s">
         <v>146</v>
       </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B7" s="5"/>
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="C7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>203</v>
+      <c r="B8" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="C8" t="s">
         <v>146</v>
       </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>204</v>
+        <v>115</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="C9" t="s">
         <v>146</v>
       </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
-        <v>205</v>
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="C10" t="s">
         <v>146</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>206</v>
+      <c r="B11" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="C11" t="s">
         <v>146</v>
@@ -4980,24 +4977,21 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>207</v>
+        <v>192</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="C12" t="s">
         <v>146</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>208</v>
+      <c r="B13" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="C13" t="s">
         <v>146</v>
@@ -5008,21 +5002,24 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>209</v>
+        <v>115</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="C14" t="s">
         <v>146</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>210</v>
+      <c r="B15" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="C15" t="s">
         <v>146</v>
@@ -5031,12 +5028,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>211</v>
+      <c r="B16" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="C16" t="s">
         <v>146</v>
@@ -5046,76 +5043,73 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>212</v>
+      <c r="B17" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="C17" t="s">
         <v>146</v>
       </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>213</v>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="C18" t="s">
         <v>146</v>
       </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="4" t="s">
-        <v>214</v>
+      <c r="B19" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="C19" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="4" t="s">
-        <v>215</v>
+      <c r="B20" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="C20" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="4" t="s">
-        <v>216</v>
+      <c r="B21" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C21" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="4" t="s">
-        <v>217</v>
+      <c r="B22" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="C22" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="4" t="s">
-        <v>27</v>
+      <c r="A23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C23" t="s">
         <v>146</v>
       </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="4" t="s">
-        <v>218</v>
+      <c r="A24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="C24" t="s">
         <v>146</v>
@@ -5123,24 +5117,18 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>178</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>13</v>
+        <v>177</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="C25" t="s">
         <v>146</v>
       </c>
-      <c r="D25" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>177</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>219</v>
+      <c r="B26" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="C26" t="s">
         <v>146</v>
@@ -5148,18 +5136,21 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>177</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>220</v>
+        <v>115</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>222</v>
       </c>
       <c r="C27" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B28" s="4" t="s">
-        <v>221</v>
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B28" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="C28" t="s">
         <v>146</v>
@@ -5167,43 +5158,49 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>222</v>
+        <v>176</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="C29" t="s">
         <v>146</v>
       </c>
-      <c r="D29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B30" s="4" t="s">
-        <v>223</v>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C30" t="s">
         <v>146</v>
       </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>176</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>176</v>
+        <v>187</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C31" t="s">
         <v>146</v>
       </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>186</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>69</v>
+        <v>183</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C32" t="s">
         <v>146</v>
@@ -5214,10 +5211,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>187</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>58</v>
+        <v>181</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="C33" t="s">
         <v>146</v>
@@ -5228,10 +5225,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>183</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>56</v>
+        <v>185</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="C34" t="s">
         <v>146</v>
@@ -5242,10 +5239,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>181</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>224</v>
+        <v>115</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="C35" t="s">
         <v>146</v>
@@ -5256,10 +5253,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>185</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>225</v>
+        <v>188</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="C36" t="s">
         <v>146</v>
@@ -5270,10 +5267,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>115</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>64</v>
+        <v>73</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="C37" t="s">
         <v>146</v>
@@ -5284,10 +5281,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>188</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>226</v>
+        <v>135</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="C38" t="s">
         <v>146</v>
@@ -5298,10 +5295,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>227</v>
+        <v>115</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="C39" t="s">
         <v>146</v>
@@ -5312,24 +5309,21 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>135</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>135</v>
+        <v>174</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="C40" t="s">
         <v>146</v>
       </c>
-      <c r="D40" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>228</v>
+        <v>179</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C41" t="s">
         <v>146</v>
@@ -5340,49 +5334,46 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>174</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="C42" t="s">
         <v>146</v>
       </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>179</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>19</v>
+        <v>180</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="C43" t="s">
         <v>146</v>
       </c>
-      <c r="D43" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>182</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>229</v>
+        <v>193</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="C44" t="s">
         <v>146</v>
       </c>
-      <c r="D44" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>180</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>180</v>
+        <v>194</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="C45" t="s">
         <v>146</v>
@@ -5390,10 +5381,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>193</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>230</v>
+        <v>195</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="C46" t="s">
         <v>146</v>
@@ -5401,10 +5392,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>194</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>231</v>
+        <v>196</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="C47" t="s">
         <v>146</v>
@@ -5412,10 +5403,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>195</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>232</v>
+        <v>197</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="C48" t="s">
         <v>146</v>
@@ -5423,10 +5414,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>196</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>233</v>
+        <v>198</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="C49" t="s">
         <v>146</v>
@@ -5434,21 +5425,18 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>197</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>234</v>
+        <v>199</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="C50" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>198</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>235</v>
+      <c r="B51" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="C51" t="s">
         <v>146</v>
@@ -5456,29 +5444,38 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>199</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>236</v>
+        <v>187</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="C52" t="s">
         <v>146</v>
       </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B53" s="4" t="s">
-        <v>237</v>
+      <c r="A53" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>239</v>
       </c>
       <c r="C53" t="s">
         <v>146</v>
       </c>
+      <c r="D53" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>187</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>238</v>
+        <v>115</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>240</v>
       </c>
       <c r="C54" t="s">
         <v>146</v>
@@ -5491,8 +5488,8 @@
       <c r="A55" t="s">
         <v>115</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>239</v>
+      <c r="B55" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="C55" t="s">
         <v>146</v>
@@ -5503,10 +5500,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>240</v>
+        <v>189</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="C56" t="s">
         <v>146</v>
@@ -5516,25 +5513,19 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>115</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>241</v>
+      <c r="B57" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="C57" t="s">
         <v>146</v>
       </c>
-      <c r="D57" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>189</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>242</v>
+        <v>115</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="C58" t="s">
         <v>146</v>
@@ -5544,76 +5535,73 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B59" s="4" t="s">
-        <v>243</v>
+      <c r="A59" t="s">
+        <v>190</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>245</v>
       </c>
       <c r="C59" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>244</v>
+      <c r="B60" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="C60" t="s">
         <v>146</v>
       </c>
-      <c r="D60" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>190</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>245</v>
+      <c r="B61" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="C61" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B62" s="4" t="s">
-        <v>246</v>
+      <c r="B62" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="C62" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B63" s="4" t="s">
-        <v>72</v>
+      <c r="B63" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="C63" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B64" s="4" t="s">
-        <v>247</v>
+      <c r="A64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C64" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B65" s="4" t="s">
-        <v>248</v>
+      <c r="A65" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="C65" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>46</v>
+      <c r="B66" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="C66" t="s">
         <v>146</v>
@@ -5621,31 +5609,12 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>184</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>249</v>
+        <v>175</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B68" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C68" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>175</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="C69" t="s">
         <v>146</v>
       </c>
     </row>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC57978-F3B5-4A36-8573-78E38382A582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BD0552-2625-408E-B751-5B17420BCBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" firstSheet="1" activeTab="3" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
@@ -619,7 +619,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="253">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -1375,6 +1375,9 @@
   </si>
   <si>
     <t>Product Title</t>
+  </si>
+  <si>
+    <t>HSN Code</t>
   </si>
 </sst>
 </file>
@@ -4899,6 +4902,9 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B5" s="4"/>
+      <c r="C5" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -5075,6 +5081,9 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>252</v>
+      </c>
       <c r="B21" s="3" t="s">
         <v>27</v>
       </c>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BD0552-2625-408E-B751-5B17420BCBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981A63EA-0E17-4B41-A775-66A427136793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" firstSheet="1" activeTab="3" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
@@ -619,7 +619,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="254">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -1378,6 +1378,9 @@
   </si>
   <si>
     <t>HSN Code</t>
+  </si>
+  <si>
+    <t>Blank</t>
   </si>
 </sst>
 </file>
@@ -4901,7 +4904,9 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>253</v>
+      </c>
       <c r="C5" t="s">
         <v>146</v>
       </c>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981A63EA-0E17-4B41-A775-66A427136793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178A3B5B-E335-4C98-BA0E-AEBCFBA473D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" firstSheet="1" activeTab="3" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" firstSheet="1" activeTab="4" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping-Dresses" sheetId="22" r:id="rId1"/>
     <sheet name="Mapping-Shorts" sheetId="20" r:id="rId2"/>
     <sheet name="Mapping-Track Pants" sheetId="5" r:id="rId3"/>
     <sheet name="Mapping-Tshirts" sheetId="6" r:id="rId4"/>
-    <sheet name="Mapping-Tops" sheetId="13" r:id="rId5"/>
-    <sheet name="Mapping-Clothing Set" sheetId="18" r:id="rId6"/>
+    <sheet name="Mapping-KidsTshirts" sheetId="23" r:id="rId5"/>
+    <sheet name="Mapping-Tops" sheetId="13" r:id="rId6"/>
+    <sheet name="Mapping-Clothing Set" sheetId="18" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Shorts'!$A$1:$E$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mapping-Tops'!$A$1:$E$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Mapping-Tops'!$A$1:$E$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mapping-Track Pants'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mapping-Tshirts'!$A$2:$E$67</definedName>
   </definedNames>
@@ -619,7 +620,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="254">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -5638,6 +5639,797 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6518D4-0A2E-49FF-AFAB-F9544B97D6F3}">
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>252</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C24" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B28" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>146</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" t="s">
+        <v>146</v>
+      </c>
+      <c r="D36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>182</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>180</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>194</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>195</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>196</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C48" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>198</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B51" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C52" t="s">
+        <v>146</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C54" t="s">
+        <v>146</v>
+      </c>
+      <c r="D54" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>189</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C56" t="s">
+        <v>146</v>
+      </c>
+      <c r="D56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B57" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C57" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C58" t="s">
+        <v>146</v>
+      </c>
+      <c r="D58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>190</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B60" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C60" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B61" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B62" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B63" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C63" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C65" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B66" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C66" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>175</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C67" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039369EB-329E-44CC-AE44-2766452032F2}">
   <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6683,7 +7475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52958128-2114-48CA-BA8D-DEBA69FFA9A3}">
   <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A67DF1-D2F1-424C-A7EC-8A242CA43DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A19BE4A-7E0D-4D58-A01B-CF1A81C98BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping-Tshirts" sheetId="6" r:id="rId1"/>
-    <sheet name="Mapping-KidsTshirts" sheetId="23" r:id="rId2"/>
+    <sheet name="Mapping-Kids T-shirt" sheetId="23" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-KidsTshirts'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids T-shirt'!$A$1:$E$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping-Tshirts'!$A$2:$E$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="114">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>Flipkart Template Column</t>
+  </si>
+  <si>
+    <t>Kids T-shirt</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1587,7 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1595,7 +1598,7 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1604,7 +1607,7 @@
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1613,7 +1616,7 @@
         <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1624,7 +1627,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1638,7 +1641,7 @@
         <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1647,7 +1650,7 @@
         <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1658,7 +1661,7 @@
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1672,7 +1675,7 @@
         <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1686,7 +1689,7 @@
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1700,7 +1703,7 @@
         <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -1711,7 +1714,7 @@
         <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -1725,7 +1728,7 @@
         <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -1739,7 +1742,7 @@
         <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -1753,7 +1756,7 @@
         <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -1765,7 +1768,7 @@
         <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1774,7 +1777,7 @@
         <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1783,7 +1786,7 @@
         <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1792,7 +1795,7 @@
         <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1803,7 +1806,7 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1812,7 +1815,7 @@
         <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1823,7 +1826,7 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -1837,7 +1840,7 @@
         <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1848,7 +1851,7 @@
         <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1857,7 +1860,7 @@
         <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1868,7 +1871,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -1880,7 +1883,7 @@
         <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1891,7 +1894,7 @@
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1902,7 +1905,7 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -1916,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
@@ -1930,7 +1933,7 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -1944,7 +1947,7 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
@@ -1958,7 +1961,7 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
@@ -1972,7 +1975,7 @@
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
@@ -1986,7 +1989,7 @@
         <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
@@ -2000,7 +2003,7 @@
         <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -2011,7 +2014,7 @@
         <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -2025,7 +2028,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -2039,7 +2042,7 @@
         <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -2050,7 +2053,7 @@
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -2064,7 +2067,7 @@
         <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2075,7 +2078,7 @@
         <v>102</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2089,7 +2092,7 @@
         <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -2100,7 +2103,7 @@
         <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2111,7 +2114,7 @@
         <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -2122,7 +2125,7 @@
         <v>79</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -2133,7 +2136,7 @@
         <v>80</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -2142,7 +2145,7 @@
         <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -2153,7 +2156,7 @@
         <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -2165,7 +2168,7 @@
         <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2174,7 +2177,7 @@
         <v>105</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2183,7 +2186,7 @@
         <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2194,7 +2197,7 @@
         <v>85</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
@@ -2206,7 +2209,7 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -2215,7 +2218,7 @@
         <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -2224,7 +2227,7 @@
         <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -2235,7 +2238,7 @@
         <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -2249,7 +2252,7 @@
         <v>108</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -2258,7 +2261,7 @@
         <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -2269,7 +2272,7 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -2280,7 +2283,7 @@
         <v>96</v>
       </c>
       <c r="C62" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -2289,7 +2292,7 @@
         <v>97</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -2298,7 +2301,7 @@
         <v>90</v>
       </c>
       <c r="C64" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -2307,7 +2310,7 @@
         <v>110</v>
       </c>
       <c r="C65" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -2316,7 +2319,7 @@
         <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -2325,7 +2328,7 @@
         <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A19BE4A-7E0D-4D58-A01B-CF1A81C98BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127C1691-4B95-4EA2-874F-440B6E9C66E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping-Tshirts" sheetId="6" r:id="rId1"/>
-    <sheet name="Mapping-Kids T-shirt" sheetId="23" r:id="rId2"/>
+    <sheet name="Mapping-Kids Tshirts" sheetId="23" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids T-shirt'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids Tshirts'!$A$1:$E$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping-Tshirts'!$A$2:$E$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="113">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -380,9 +380,6 @@
   </si>
   <si>
     <t>Flipkart Template Column</t>
-  </si>
-  <si>
-    <t>Kids T-shirt</t>
   </si>
 </sst>
 </file>
@@ -423,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -431,6 +428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1586,8 +1584,8 @@
       <c r="B2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
-        <v>113</v>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1597,8 +1595,8 @@
       <c r="B3" t="s">
         <v>48</v>
       </c>
-      <c r="C3" t="s">
-        <v>113</v>
+      <c r="C3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1606,8 +1604,8 @@
       <c r="B4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
-        <v>113</v>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1615,8 +1613,8 @@
       <c r="B5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C5" t="s">
-        <v>113</v>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1626,8 +1624,8 @@
       <c r="B6" t="s">
         <v>50</v>
       </c>
-      <c r="C6" t="s">
-        <v>113</v>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1640,8 +1638,8 @@
       <c r="B7" t="s">
         <v>51</v>
       </c>
-      <c r="C7" t="s">
-        <v>113</v>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1649,8 +1647,8 @@
       <c r="B8" t="s">
         <v>52</v>
       </c>
-      <c r="C8" t="s">
-        <v>113</v>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1660,8 +1658,8 @@
       <c r="B9" t="s">
         <v>53</v>
       </c>
-      <c r="C9" t="s">
-        <v>113</v>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1674,8 +1672,8 @@
       <c r="B10" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
-        <v>113</v>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1688,8 +1686,8 @@
       <c r="B11" t="s">
         <v>55</v>
       </c>
-      <c r="C11" t="s">
-        <v>113</v>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1702,8 +1700,8 @@
       <c r="B12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
-        <v>113</v>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -1713,8 +1711,8 @@
       <c r="B13" t="s">
         <v>57</v>
       </c>
-      <c r="C13" t="s">
-        <v>113</v>
+      <c r="C13" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -1727,8 +1725,8 @@
       <c r="B14" t="s">
         <v>58</v>
       </c>
-      <c r="C14" t="s">
-        <v>113</v>
+      <c r="C14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -1741,8 +1739,8 @@
       <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="C15" t="s">
-        <v>113</v>
+      <c r="C15" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -1755,8 +1753,8 @@
       <c r="B16" t="s">
         <v>60</v>
       </c>
-      <c r="C16" t="s">
-        <v>113</v>
+      <c r="C16" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -1767,8 +1765,8 @@
       <c r="B17" t="s">
         <v>61</v>
       </c>
-      <c r="C17" t="s">
-        <v>113</v>
+      <c r="C17" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1776,8 +1774,8 @@
       <c r="B18" t="s">
         <v>62</v>
       </c>
-      <c r="C18" t="s">
-        <v>113</v>
+      <c r="C18" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1785,8 +1783,8 @@
       <c r="B19" t="s">
         <v>63</v>
       </c>
-      <c r="C19" t="s">
-        <v>113</v>
+      <c r="C19" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1794,8 +1792,8 @@
       <c r="B20" t="s">
         <v>64</v>
       </c>
-      <c r="C20" t="s">
-        <v>113</v>
+      <c r="C20" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1805,8 +1803,8 @@
       <c r="B21" t="s">
         <v>6</v>
       </c>
-      <c r="C21" t="s">
-        <v>113</v>
+      <c r="C21" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1814,8 +1812,8 @@
       <c r="B22" t="s">
         <v>65</v>
       </c>
-      <c r="C22" t="s">
-        <v>113</v>
+      <c r="C22" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1825,8 +1823,8 @@
       <c r="B23" t="s">
         <v>3</v>
       </c>
-      <c r="C23" t="s">
-        <v>113</v>
+      <c r="C23" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -1839,8 +1837,8 @@
       <c r="B24" t="s">
         <v>66</v>
       </c>
-      <c r="C24" t="s">
-        <v>113</v>
+      <c r="C24" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1850,8 +1848,8 @@
       <c r="B25" t="s">
         <v>67</v>
       </c>
-      <c r="C25" t="s">
-        <v>113</v>
+      <c r="C25" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1859,8 +1857,8 @@
       <c r="B26" t="s">
         <v>68</v>
       </c>
-      <c r="C26" t="s">
-        <v>113</v>
+      <c r="C26" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1870,8 +1868,8 @@
       <c r="B27" t="s">
         <v>69</v>
       </c>
-      <c r="C27" t="s">
-        <v>113</v>
+      <c r="C27" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -1882,8 +1880,8 @@
       <c r="B28" t="s">
         <v>70</v>
       </c>
-      <c r="C28" t="s">
-        <v>113</v>
+      <c r="C28" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1893,8 +1891,8 @@
       <c r="B29" t="s">
         <v>23</v>
       </c>
-      <c r="C29" t="s">
-        <v>113</v>
+      <c r="C29" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1904,8 +1902,8 @@
       <c r="B30" t="s">
         <v>71</v>
       </c>
-      <c r="C30" t="s">
-        <v>113</v>
+      <c r="C30" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -1918,8 +1916,8 @@
       <c r="B31" t="s">
         <v>9</v>
       </c>
-      <c r="C31" t="s">
-        <v>113</v>
+      <c r="C31" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
@@ -1932,8 +1930,8 @@
       <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" t="s">
-        <v>113</v>
+      <c r="C32" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -1946,8 +1944,8 @@
       <c r="B33" t="s">
         <v>18</v>
       </c>
-      <c r="C33" t="s">
-        <v>113</v>
+      <c r="C33" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
@@ -1960,8 +1958,8 @@
       <c r="B34" t="s">
         <v>11</v>
       </c>
-      <c r="C34" t="s">
-        <v>113</v>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
@@ -1974,8 +1972,8 @@
       <c r="B35" t="s">
         <v>12</v>
       </c>
-      <c r="C35" t="s">
-        <v>113</v>
+      <c r="C35" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
@@ -1988,8 +1986,8 @@
       <c r="B36" t="s">
         <v>32</v>
       </c>
-      <c r="C36" t="s">
-        <v>113</v>
+      <c r="C36" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
@@ -2002,8 +2000,8 @@
       <c r="B37" t="s">
         <v>101</v>
       </c>
-      <c r="C37" t="s">
-        <v>113</v>
+      <c r="C37" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -2013,8 +2011,8 @@
       <c r="B38" t="s">
         <v>15</v>
       </c>
-      <c r="C38" t="s">
-        <v>113</v>
+      <c r="C38" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -2027,8 +2025,8 @@
       <c r="B39" t="s">
         <v>74</v>
       </c>
-      <c r="C39" t="s">
-        <v>113</v>
+      <c r="C39" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -2041,8 +2039,8 @@
       <c r="B40" t="s">
         <v>21</v>
       </c>
-      <c r="C40" t="s">
-        <v>113</v>
+      <c r="C40" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -2052,8 +2050,8 @@
       <c r="B41" t="s">
         <v>26</v>
       </c>
-      <c r="C41" t="s">
-        <v>113</v>
+      <c r="C41" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -2066,8 +2064,8 @@
       <c r="B42" t="s">
         <v>27</v>
       </c>
-      <c r="C42" t="s">
-        <v>113</v>
+      <c r="C42" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2077,8 +2075,8 @@
       <c r="B43" t="s">
         <v>102</v>
       </c>
-      <c r="C43" t="s">
-        <v>113</v>
+      <c r="C43" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2091,8 +2089,8 @@
       <c r="B44" t="s">
         <v>103</v>
       </c>
-      <c r="C44" t="s">
-        <v>113</v>
+      <c r="C44" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -2102,8 +2100,8 @@
       <c r="B45" t="s">
         <v>77</v>
       </c>
-      <c r="C45" t="s">
-        <v>113</v>
+      <c r="C45" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2113,8 +2111,8 @@
       <c r="B46" t="s">
         <v>78</v>
       </c>
-      <c r="C46" t="s">
-        <v>113</v>
+      <c r="C46" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -2124,8 +2122,8 @@
       <c r="B47" t="s">
         <v>79</v>
       </c>
-      <c r="C47" t="s">
-        <v>113</v>
+      <c r="C47" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -2135,8 +2133,8 @@
       <c r="B48" t="s">
         <v>80</v>
       </c>
-      <c r="C48" t="s">
-        <v>113</v>
+      <c r="C48" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -2144,8 +2142,8 @@
       <c r="B49" t="s">
         <v>93</v>
       </c>
-      <c r="C49" t="s">
-        <v>113</v>
+      <c r="C49" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -2155,8 +2153,8 @@
       <c r="B50" t="s">
         <v>91</v>
       </c>
-      <c r="C50" t="s">
-        <v>113</v>
+      <c r="C50" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -2167,8 +2165,8 @@
       <c r="B51" t="s">
         <v>104</v>
       </c>
-      <c r="C51" t="s">
-        <v>113</v>
+      <c r="C51" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2176,8 +2174,8 @@
       <c r="B52" t="s">
         <v>105</v>
       </c>
-      <c r="C52" t="s">
-        <v>113</v>
+      <c r="C52" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2185,8 +2183,8 @@
       <c r="B53" t="s">
         <v>106</v>
       </c>
-      <c r="C53" t="s">
-        <v>113</v>
+      <c r="C53" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2196,8 +2194,8 @@
       <c r="B54" t="s">
         <v>85</v>
       </c>
-      <c r="C54" t="s">
-        <v>113</v>
+      <c r="C54" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
@@ -2208,8 +2206,8 @@
       <c r="B55" t="s">
         <v>13</v>
       </c>
-      <c r="C55" t="s">
-        <v>113</v>
+      <c r="C55" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -2217,8 +2215,8 @@
       <c r="B56" t="s">
         <v>94</v>
       </c>
-      <c r="C56" t="s">
-        <v>113</v>
+      <c r="C56" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -2226,8 +2224,8 @@
       <c r="B57" t="s">
         <v>107</v>
       </c>
-      <c r="C57" t="s">
-        <v>113</v>
+      <c r="C57" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -2237,8 +2235,8 @@
       <c r="B58" t="s">
         <v>89</v>
       </c>
-      <c r="C58" t="s">
-        <v>113</v>
+      <c r="C58" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -2251,8 +2249,8 @@
       <c r="B59" t="s">
         <v>108</v>
       </c>
-      <c r="C59" t="s">
-        <v>113</v>
+      <c r="C59" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -2260,8 +2258,8 @@
       <c r="B60" t="s">
         <v>109</v>
       </c>
-      <c r="C60" t="s">
-        <v>113</v>
+      <c r="C60" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -2271,8 +2269,8 @@
       <c r="B61" t="s">
         <v>8</v>
       </c>
-      <c r="C61" t="s">
-        <v>113</v>
+      <c r="C61" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -2282,8 +2280,8 @@
       <c r="B62" t="s">
         <v>96</v>
       </c>
-      <c r="C62" t="s">
-        <v>113</v>
+      <c r="C62" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -2291,8 +2289,8 @@
       <c r="B63" t="s">
         <v>97</v>
       </c>
-      <c r="C63" t="s">
-        <v>113</v>
+      <c r="C63" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -2300,8 +2298,8 @@
       <c r="B64" t="s">
         <v>90</v>
       </c>
-      <c r="C64" t="s">
-        <v>113</v>
+      <c r="C64" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -2309,8 +2307,8 @@
       <c r="B65" t="s">
         <v>110</v>
       </c>
-      <c r="C65" t="s">
-        <v>113</v>
+      <c r="C65" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -2318,8 +2316,8 @@
       <c r="B66" t="s">
         <v>111</v>
       </c>
-      <c r="C66" t="s">
-        <v>113</v>
+      <c r="C66" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -2327,8 +2325,8 @@
       <c r="B67" t="s">
         <v>95</v>
       </c>
-      <c r="C67" t="s">
-        <v>113</v>
+      <c r="C67" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\Myntra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127C1691-4B95-4EA2-874F-440B6E9C66E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CC0450-6F54-491C-9E43-0A6AEAFBCAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Mapping-Kids Tshirts" sheetId="23" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids Tshirts'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapping-Kids Tshirts'!$A$1:$D$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping-Tshirts'!$A$2:$E$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="114">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>Flipkart Template Column</t>
+  </si>
+  <si>
+    <t>Kids Tshirts</t>
   </si>
 </sst>
 </file>
@@ -420,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -428,7 +431,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,6 +771,7 @@
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1559,7 +1562,7 @@
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1584,8 +1587,8 @@
       <c r="B2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
+      <c r="C2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1595,8 +1598,8 @@
       <c r="B3" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
+      <c r="C3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1604,8 +1607,8 @@
       <c r="B4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
+      <c r="C4" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1613,19 +1616,19 @@
       <c r="B5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
+      <c r="C5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
+      <c r="C6" t="s">
+        <v>113</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1638,8 +1641,8 @@
       <c r="B7" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
+      <c r="C7" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1647,47 +1650,47 @@
       <c r="B8" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
+      <c r="C8" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
+      <c r="C9" t="s">
+        <v>113</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
+      <c r="C10" t="s">
+        <v>113</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>19</v>
+      <c r="C11" t="s">
+        <v>113</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1700,61 +1703,61 @@
       <c r="B12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>19</v>
+      <c r="C12" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>19</v>
+      <c r="C13" t="s">
+        <v>113</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>19</v>
+      <c r="C14" t="s">
+        <v>113</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>19</v>
+      <c r="C15" t="s">
+        <v>113</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>19</v>
+      <c r="C16" t="s">
+        <v>113</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -1765,8 +1768,8 @@
       <c r="B17" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>19</v>
+      <c r="C17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1774,8 +1777,8 @@
       <c r="B18" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>19</v>
+      <c r="C18" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1783,8 +1786,8 @@
       <c r="B19" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>19</v>
+      <c r="C19" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1792,8 +1795,8 @@
       <c r="B20" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>19</v>
+      <c r="C20" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1803,8 +1806,8 @@
       <c r="B21" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>19</v>
+      <c r="C21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1812,8 +1815,8 @@
       <c r="B22" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>19</v>
+      <c r="C22" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1823,8 +1826,8 @@
       <c r="B23" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>19</v>
+      <c r="C23" t="s">
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -1837,8 +1840,8 @@
       <c r="B24" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>19</v>
+      <c r="C24" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1848,8 +1851,8 @@
       <c r="B25" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>19</v>
+      <c r="C25" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1857,19 +1860,19 @@
       <c r="B26" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>19</v>
+      <c r="C26" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>17</v>
       </c>
       <c r="B27" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>19</v>
+      <c r="C27" t="s">
+        <v>113</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -1880,8 +1883,8 @@
       <c r="B28" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>19</v>
+      <c r="C28" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1891,8 +1894,8 @@
       <c r="B29" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>19</v>
+      <c r="C29" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1902,8 +1905,8 @@
       <c r="B30" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>19</v>
+      <c r="C30" t="s">
+        <v>113</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -1916,8 +1919,8 @@
       <c r="B31" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>19</v>
+      <c r="C31" t="s">
+        <v>113</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
@@ -1930,8 +1933,8 @@
       <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>19</v>
+      <c r="C32" t="s">
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -1944,22 +1947,22 @@
       <c r="B33" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>19</v>
+      <c r="C33" t="s">
+        <v>113</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>17</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>19</v>
+      <c r="C34" t="s">
+        <v>113</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
@@ -1972,8 +1975,8 @@
       <c r="B35" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>19</v>
+      <c r="C35" t="s">
+        <v>113</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
@@ -1986,8 +1989,8 @@
       <c r="B36" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>19</v>
+      <c r="C36" t="s">
+        <v>113</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
@@ -2000,8 +2003,8 @@
       <c r="B37" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>19</v>
+      <c r="C37" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -2011,8 +2014,8 @@
       <c r="B38" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>19</v>
+      <c r="C38" t="s">
+        <v>113</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -2025,8 +2028,8 @@
       <c r="B39" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>19</v>
+      <c r="C39" t="s">
+        <v>113</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -2039,8 +2042,8 @@
       <c r="B40" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>19</v>
+      <c r="C40" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -2050,8 +2053,8 @@
       <c r="B41" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>19</v>
+      <c r="C41" t="s">
+        <v>113</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -2064,8 +2067,8 @@
       <c r="B42" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>19</v>
+      <c r="C42" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2075,8 +2078,8 @@
       <c r="B43" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>19</v>
+      <c r="C43" t="s">
+        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2089,8 +2092,8 @@
       <c r="B44" t="s">
         <v>103</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>19</v>
+      <c r="C44" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -2100,8 +2103,8 @@
       <c r="B45" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>19</v>
+      <c r="C45" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2111,8 +2114,8 @@
       <c r="B46" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>19</v>
+      <c r="C46" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -2122,8 +2125,8 @@
       <c r="B47" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>19</v>
+      <c r="C47" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -2133,8 +2136,8 @@
       <c r="B48" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>19</v>
+      <c r="C48" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -2142,19 +2145,19 @@
       <c r="B49" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>19</v>
+      <c r="C49" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>17</v>
       </c>
       <c r="B50" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>19</v>
+      <c r="C50" t="s">
+        <v>113</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -2165,8 +2168,8 @@
       <c r="B51" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>19</v>
+      <c r="C51" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2174,8 +2177,8 @@
       <c r="B52" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>19</v>
+      <c r="C52" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2183,8 +2186,8 @@
       <c r="B53" t="s">
         <v>106</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>19</v>
+      <c r="C53" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2194,8 +2197,8 @@
       <c r="B54" t="s">
         <v>85</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>19</v>
+      <c r="C54" t="s">
+        <v>113</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
@@ -2206,8 +2209,8 @@
       <c r="B55" t="s">
         <v>13</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>19</v>
+      <c r="C55" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -2215,8 +2218,8 @@
       <c r="B56" t="s">
         <v>94</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>19</v>
+      <c r="C56" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -2224,8 +2227,8 @@
       <c r="B57" t="s">
         <v>107</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>19</v>
+      <c r="C57" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -2235,8 +2238,8 @@
       <c r="B58" t="s">
         <v>89</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>19</v>
+      <c r="C58" t="s">
+        <v>113</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -2249,8 +2252,8 @@
       <c r="B59" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>19</v>
+      <c r="C59" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -2258,8 +2261,8 @@
       <c r="B60" t="s">
         <v>109</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>19</v>
+      <c r="C60" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -2269,8 +2272,8 @@
       <c r="B61" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>19</v>
+      <c r="C61" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -2280,8 +2283,8 @@
       <c r="B62" t="s">
         <v>96</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>19</v>
+      <c r="C62" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -2289,8 +2292,8 @@
       <c r="B63" t="s">
         <v>97</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>19</v>
+      <c r="C63" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -2298,8 +2301,8 @@
       <c r="B64" t="s">
         <v>90</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>19</v>
+      <c r="C64" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -2307,8 +2310,8 @@
       <c r="B65" t="s">
         <v>110</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>19</v>
+      <c r="C65" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -2316,8 +2319,8 @@
       <c r="B66" t="s">
         <v>111</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>19</v>
+      <c r="C66" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -2325,8 +2328,8 @@
       <c r="B67" t="s">
         <v>95</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>19</v>
+      <c r="C67" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CC0450-6F54-491C-9E43-0A6AEAFBCAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2237ACFF-CE5B-432E-BF25-8A1EFA91064B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="115">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -383,6 +383,9 @@
   </si>
   <si>
     <t>Kids Tshirts</t>
+  </si>
+  <si>
+    <t>Flipkart Category</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1577,7 @@
         <v>112</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1622,7 +1625,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
@@ -1656,7 +1659,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
@@ -1670,7 +1673,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
         <v>54</v>
@@ -1684,7 +1687,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
@@ -1709,7 +1712,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
         <v>57</v>
@@ -1723,7 +1726,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
@@ -1737,7 +1740,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
         <v>59</v>
@@ -1751,7 +1754,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
         <v>60</v>
@@ -1866,7 +1869,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B27" t="s">
         <v>69</v>
@@ -1956,7 +1959,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
@@ -2151,7 +2154,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="B50" t="s">
         <v>91</v>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2237ACFF-CE5B-432E-BF25-8A1EFA91064B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDD1EF5-A75A-4EFC-8470-7E1A61B8291A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>

--- a/config/Flipkart_instruction.xlsx
+++ b/config/Flipkart_instruction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDD1EF5-A75A-4EFC-8470-7E1A61B8291A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26307522-916E-4D0E-A467-9C2939720DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" activeTab="1" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="763" xr2:uid="{7CCB67D7-A8F6-4AE5-994C-FCC3DF1A31CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping-Tshirts" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="114">
   <si>
     <t>Myntra Template Column</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>Character</t>
-  </si>
-  <si>
-    <t>Value</t>
   </si>
   <si>
     <t>Final Category</t>
@@ -768,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F62085-80E4-4F8B-99A1-7536229413A5}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
@@ -777,7 +774,7 @@
     <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -785,190 +782,187 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B4" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="1" t="s">
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -976,64 +970,64 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -1041,43 +1035,43 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -1085,32 +1079,32 @@
     </row>
     <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -1118,13 +1112,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
@@ -1132,13 +1126,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -1146,13 +1140,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
@@ -1160,13 +1154,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
@@ -1174,13 +1168,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
@@ -1188,13 +1182,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
@@ -1205,10 +1199,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
@@ -1216,13 +1210,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -1230,13 +1224,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -1244,24 +1238,24 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -1269,13 +1263,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -1283,109 +1277,109 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -1393,13 +1387,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -1407,13 +1401,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
@@ -1421,13 +1415,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
@@ -1435,13 +1429,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
@@ -1449,21 +1443,21 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -1471,21 +1465,21 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B60" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -1493,23 +1487,23 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B63" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -1520,37 +1514,37 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1564,7 +1558,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1574,443 +1568,443 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
-      </c>
       <c r="C3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
         <v>52</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>53</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>113</v>
       </c>
-      <c r="D9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>113</v>
       </c>
-      <c r="D10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>113</v>
       </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>113</v>
       </c>
-      <c r="D13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>59</v>
       </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
         <v>66</v>
       </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>67</v>
-      </c>
       <c r="C25" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" t="s">
         <v>68</v>
       </c>
-      <c r="C26" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
         <v>70</v>
       </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>113</v>
-      </c>
-      <c r="D32" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>114</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
@@ -2018,71 +2012,71 @@
         <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>26</v>
       </c>
-      <c r="C41" t="s">
-        <v>113</v>
-      </c>
-      <c r="D41" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" t="s">
-        <v>27</v>
-      </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2090,77 +2084,77 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -2169,39 +2163,39 @@
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
@@ -2213,36 +2207,36 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C56" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C57" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -2250,22 +2244,22 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C59" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -2276,63 +2270,63 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C66" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
